--- a/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/ShopItems.xlsx
+++ b/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/ShopItems.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13515" tabRatio="500" activeTab="7"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="500" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="IDs" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="120">
   <si>
     <t>Chests</t>
   </si>
@@ -494,6 +494,12 @@
   </si>
   <si>
     <t>rewardValue</t>
+  </si>
+  <si>
+    <t>okma</t>
+  </si>
+  <si>
+    <t>tét</t>
   </si>
   <si>
     <t>CURRENCY_COMMON_PART</t>
@@ -1188,12 +1194,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1576,7 +1582,7 @@
     <col min="5" max="5" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="4:5">
+    <row r="5" spans="1:5">
       <c r="D5" t="s">
         <v>8</v>
       </c>
@@ -1634,7 +1640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="4:5">
+    <row r="6" spans="1:5">
       <c r="D6" t="s">
         <v>9</v>
       </c>
@@ -1642,7 +1648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="4:5">
+    <row r="7" spans="1:5">
       <c r="D7" t="s">
         <v>10</v>
       </c>
@@ -1650,7 +1656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="4:5">
+    <row r="8" spans="1:5">
       <c r="D8" t="s">
         <v>11</v>
       </c>
@@ -1658,7 +1664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="4:5">
+    <row r="9" spans="1:5">
       <c r="D9" t="s">
         <v>12</v>
       </c>
@@ -1666,7 +1672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="4:5">
+    <row r="10" spans="1:5">
       <c r="D10" t="s">
         <v>13</v>
       </c>
@@ -1674,7 +1680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="4:5">
+    <row r="11" spans="1:5">
       <c r="D11" t="s">
         <v>14</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2477,7 +2483,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2661,7 +2667,7 @@
     <col min="6" max="6" width="15.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>73</v>
       </c>
@@ -2910,7 +2916,7 @@
     <col min="6" max="6" width="14.8571428571429" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:8">
+    <row r="9" s="3" customFormat="1" spans="1:9">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:8">
+    <row r="14" s="3" customFormat="1" spans="1:9">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3314,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:8">
+    <row r="15" s="3" customFormat="1" spans="1:9">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3532,8 +3538,8 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.28571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.4285714285714" customWidth="1"/>
@@ -3541,7 +3547,7 @@
     <col min="4" max="4" width="13.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -3554,8 +3560,11 @@
       <c r="D1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3566,7 +3575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3580,7 +3589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3593,8 +3602,11 @@
       <c r="D4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3602,18 +3614,18 @@
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -3622,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3633,7 +3645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3647,7 +3659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3661,7 +3673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3669,18 +3681,18 @@
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2</v>
